--- a/Min_Diagramportal/data_pipeline/Styrfil_Manad.xlsx
+++ b/Min_Diagramportal/data_pipeline/Styrfil_Manad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SR-Disk-2\Hem0006\jimlin\Desktop\Mina_Befolknings_Dashboards\Min_Diagramportal\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B54F58-9D23-4D90-95A1-9E5248158FFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41207E1A-95DA-4CE5-BDB9-DF0F8D575922}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17505" xr2:uid="{C637E13A-B939-402F-8D74-59F518012C1F}"/>
   </bookViews>
@@ -5389,7 +5389,7 @@
         <v>275</v>
       </c>
       <c r="P61" s="5" t="s">
-        <v>28</v>
+        <v>267</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>28</v>
@@ -6193,10 +6193,10 @@
         <v>-0.05</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="N73" t="s">
         <v>28</v>
@@ -6223,7 +6223,7 @@
         <v>28</v>
       </c>
       <c r="V73" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.25">
@@ -6947,10 +6947,10 @@
         <v>28</v>
       </c>
       <c r="N84" t="s">
-        <v>28</v>
+        <v>199</v>
       </c>
       <c r="O84" t="s">
-        <v>28</v>
+        <v>275</v>
       </c>
       <c r="P84" s="5" t="s">
         <v>28</v>
@@ -7756,7 +7756,7 @@
       <c r="K96" s="3">
         <v>-0.05</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="L96" t="s">
         <v>28</v>
       </c>
       <c r="M96" s="3" t="s">

--- a/Min_Diagramportal/data_pipeline/Styrfil_Manad.xlsx
+++ b/Min_Diagramportal/data_pipeline/Styrfil_Manad.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SR-Disk-2\Hem0006\jimlin\Desktop\Mina_Befolknings_Dashboards\Min_Diagramportal\data_pipeline\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Mina_Befolknings_Dashboards\Min_Diagramportal\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41207E1A-95DA-4CE5-BDB9-DF0F8D575922}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D04F074-775C-47DB-8790-A96C5EF3A8B4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17505" xr2:uid="{C637E13A-B939-402F-8D74-59F518012C1F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2335" uniqueCount="311">
   <si>
     <t>Område</t>
   </si>
@@ -877,16 +877,109 @@
   </si>
   <si>
     <t>Ej_självförsörjande_inrikes_födda_20-64_år, Ej_självförsörjande_utrikes_födda_20-64_år</t>
+  </si>
+  <si>
+    <t>Struktur_Totalt</t>
+  </si>
+  <si>
+    <t>Struktur_Ungdomar</t>
+  </si>
+  <si>
+    <t>Struktur_Män</t>
+  </si>
+  <si>
+    <t>Struktur_Kvinnor</t>
+  </si>
+  <si>
+    <t>Struktur_Förgymn</t>
+  </si>
+  <si>
+    <t>Struktur_Eftergymn</t>
+  </si>
+  <si>
+    <t>Struktur_Gymn</t>
+  </si>
+  <si>
+    <t>Arbetslöshetens karaktär: Totalt</t>
+  </si>
+  <si>
+    <t>Arbetslöshetens karaktär: Utrikes födda</t>
+  </si>
+  <si>
+    <t>Arbetslöshetens karaktär: Inrikes födda</t>
+  </si>
+  <si>
+    <t>Arbetslöshetens karaktär: Män</t>
+  </si>
+  <si>
+    <t>Arbetslöshetens karaktär: Kvinnor</t>
+  </si>
+  <si>
+    <t>Arbetslöshetens karaktär: Ungdomar 18-24 år</t>
+  </si>
+  <si>
+    <t>Arbetslöshetens karaktär: Förgymnasial utbildning</t>
+  </si>
+  <si>
+    <t>Arbetslöshetens karaktär: Gymnasial utbildning</t>
+  </si>
+  <si>
+    <t>Arbetslöshetens karaktär: Eftergymnasial utbildning</t>
+  </si>
+  <si>
+    <t>Struktur_Utrikes_födda</t>
+  </si>
+  <si>
+    <t>Struktur_Inrikes_födda</t>
+  </si>
+  <si>
+    <t>Struktur_Förgymnasial_utbildning</t>
+  </si>
+  <si>
+    <t>Struktur_Gymnasial_utbildning</t>
+  </si>
+  <si>
+    <t>Struktur_Eftergymnasial_utbildning</t>
+  </si>
+  <si>
+    <t>Ojämlikhet_Utrikes_vs_Inrikes</t>
+  </si>
+  <si>
+    <t>Utrikes vs Inrikes födda</t>
+  </si>
+  <si>
+    <t>Förgymn. vs Eftergymn. U'tb.</t>
+  </si>
+  <si>
+    <t>Ojämlikhet_Förgymn_vs_Eftergymn</t>
+  </si>
+  <si>
+    <t>Orange, Blå</t>
+  </si>
+  <si>
+    <t>2%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>1%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -912,7 +1005,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -928,6 +1021,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1242,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D13EDD2-E47A-46DB-9FEA-D77EC5ED30D6}">
-  <dimension ref="A1:V113"/>
+  <dimension ref="A1:V124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -1347,7 +1441,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>28</v>
@@ -1415,7 +1509,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>28</v>
@@ -1483,7 +1577,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>28</v>
@@ -2231,7 +2325,7 @@
         <v>15</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>241</v>
@@ -2299,7 +2393,7 @@
         <v>15</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>28</v>
@@ -2367,7 +2461,7 @@
         <v>15</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>28</v>
@@ -2435,7 +2529,7 @@
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>28</v>
@@ -2503,7 +2597,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>28</v>
@@ -2571,7 +2665,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>28</v>
@@ -2639,7 +2733,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>28</v>
@@ -2707,7 +2801,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>28</v>
@@ -2775,7 +2869,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>28</v>
@@ -2843,7 +2937,7 @@
         <v>15</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>28</v>
@@ -2911,7 +3005,7 @@
         <v>15</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>28</v>
@@ -2979,7 +3073,7 @@
         <v>15</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>28</v>
@@ -3047,7 +3141,7 @@
         <v>15</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>28</v>
@@ -3115,7 +3209,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>28</v>
@@ -3183,7 +3277,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>28</v>
@@ -3251,7 +3345,7 @@
         <v>15</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>28</v>
@@ -3319,7 +3413,7 @@
         <v>15</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>28</v>
@@ -3387,7 +3481,7 @@
         <v>15</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>28</v>
@@ -3455,7 +3549,7 @@
         <v>16</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>28</v>
@@ -3523,7 +3617,7 @@
         <v>15</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>28</v>
@@ -3591,7 +3685,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>28</v>
@@ -3659,7 +3753,7 @@
         <v>16</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>28</v>
@@ -3727,7 +3821,7 @@
         <v>16</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>28</v>
@@ -3795,7 +3889,7 @@
         <v>15</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>28</v>
@@ -3863,7 +3957,7 @@
         <v>16</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>28</v>
@@ -3931,7 +4025,7 @@
         <v>15</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>28</v>
@@ -3999,7 +4093,7 @@
         <v>15</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>28</v>
@@ -4067,7 +4161,7 @@
         <v>16</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>28</v>
@@ -4135,7 +4229,7 @@
         <v>16</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>28</v>
@@ -4203,7 +4297,7 @@
         <v>15</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>28</v>
@@ -4271,7 +4365,7 @@
         <v>15</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>28</v>
@@ -4339,7 +4433,7 @@
         <v>15</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>28</v>
@@ -4407,7 +4501,7 @@
         <v>16</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>28</v>
@@ -4475,7 +4569,7 @@
         <v>16</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>28</v>
@@ -4543,7 +4637,7 @@
         <v>16</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>28</v>
@@ -4611,7 +4705,7 @@
         <v>16</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>28</v>
@@ -4679,7 +4773,7 @@
         <v>16</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>28</v>
@@ -4747,7 +4841,7 @@
         <v>16</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>28</v>
@@ -4815,7 +4909,7 @@
         <v>16</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>28</v>
@@ -4883,7 +4977,7 @@
         <v>16</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>28</v>
@@ -4951,7 +5045,7 @@
         <v>16</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>28</v>
@@ -5019,7 +5113,7 @@
         <v>16</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>28</v>
@@ -5087,7 +5181,7 @@
         <v>16</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>28</v>
@@ -5155,7 +5249,7 @@
         <v>16</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>28</v>
@@ -5223,7 +5317,7 @@
         <v>16</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>28</v>
@@ -5291,7 +5385,7 @@
         <v>16</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>240</v>
@@ -5359,7 +5453,7 @@
         <v>16</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>28</v>
@@ -5427,7 +5521,7 @@
         <v>16</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>28</v>
@@ -5448,16 +5542,16 @@
         <v>177</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="N62" t="s">
-        <v>28</v>
+        <v>278</v>
       </c>
       <c r="O62" t="s">
-        <v>28</v>
+        <v>307</v>
       </c>
       <c r="P62" s="5" t="s">
-        <v>28</v>
+        <v>267</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>28</v>
@@ -5495,7 +5589,7 @@
         <v>16</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>28</v>
@@ -5563,7 +5657,7 @@
         <v>16</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>28</v>
@@ -5631,7 +5725,7 @@
         <v>16</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>28</v>
@@ -5699,7 +5793,7 @@
         <v>16</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>28</v>
@@ -5767,7 +5861,7 @@
         <v>16</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>28</v>
@@ -5835,7 +5929,7 @@
         <v>16</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>28</v>
@@ -5903,7 +5997,7 @@
         <v>16</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>28</v>
@@ -5971,7 +6065,7 @@
         <v>16</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>28</v>
@@ -6039,7 +6133,7 @@
         <v>16</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>28</v>
@@ -6107,7 +6201,7 @@
         <v>16</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>28</v>
@@ -6175,7 +6269,7 @@
         <v>16</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>28</v>
@@ -6243,7 +6337,7 @@
         <v>16</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>28</v>
@@ -6311,7 +6405,7 @@
         <v>16</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>28</v>
@@ -6379,7 +6473,7 @@
         <v>16</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>28</v>
@@ -6447,7 +6541,7 @@
         <v>16</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>28</v>
@@ -6515,7 +6609,7 @@
         <v>16</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>240</v>
@@ -6583,7 +6677,7 @@
         <v>16</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>28</v>
@@ -6651,7 +6745,7 @@
         <v>16</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>28</v>
@@ -6719,7 +6813,7 @@
         <v>16</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>28</v>
@@ -6787,7 +6881,7 @@
         <v>16</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>28</v>
@@ -6855,7 +6949,7 @@
         <v>16</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>240</v>
@@ -6923,7 +7017,7 @@
         <v>16</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>28</v>
@@ -6991,7 +7085,7 @@
         <v>16</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>28</v>
@@ -7059,7 +7153,7 @@
         <v>16</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>28</v>
@@ -7127,7 +7221,7 @@
         <v>16</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>28</v>
@@ -7195,7 +7289,7 @@
         <v>16</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>28</v>
@@ -7263,7 +7357,7 @@
         <v>16</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>28</v>
@@ -7331,7 +7425,7 @@
         <v>16</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>28</v>
@@ -7399,7 +7493,7 @@
         <v>16</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>28</v>
@@ -7467,7 +7561,7 @@
         <v>16</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>28</v>
@@ -7535,7 +7629,7 @@
         <v>16</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>28</v>
@@ -7603,7 +7697,7 @@
         <v>16</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>28</v>
@@ -7671,7 +7765,7 @@
         <v>16</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>28</v>
@@ -7739,7 +7833,7 @@
         <v>16</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>28</v>
@@ -7807,7 +7901,7 @@
         <v>16</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>28</v>
@@ -7875,7 +7969,7 @@
         <v>16</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>28</v>
@@ -7943,7 +8037,7 @@
         <v>16</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>28</v>
@@ -8011,7 +8105,7 @@
         <v>16</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>28</v>
@@ -8079,7 +8173,7 @@
         <v>16</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>28</v>
@@ -8147,7 +8241,7 @@
         <v>16</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>28</v>
@@ -8215,7 +8309,7 @@
         <v>16</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>28</v>
@@ -8283,7 +8377,7 @@
         <v>16</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>28</v>
@@ -8351,7 +8445,7 @@
         <v>16</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>28</v>
@@ -8428,7 +8522,7 @@
         <v>28</v>
       </c>
       <c r="I106" s="4">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="J106" s="3" t="s">
         <v>28</v>
@@ -8496,7 +8590,7 @@
         <v>28</v>
       </c>
       <c r="I107" s="4">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="J107" s="3" t="s">
         <v>28</v>
@@ -8564,7 +8658,7 @@
         <v>4</v>
       </c>
       <c r="I108" s="4">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="J108" s="3" t="s">
         <v>28</v>
@@ -8632,7 +8726,7 @@
         <v>28</v>
       </c>
       <c r="I109" s="4">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="J109" s="3" t="s">
         <v>28</v>
@@ -8700,7 +8794,7 @@
         <v>28</v>
       </c>
       <c r="I110" s="4">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="J110" s="3" t="s">
         <v>28</v>
@@ -8768,7 +8862,7 @@
         <v>2</v>
       </c>
       <c r="I111" s="4">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="J111" s="3" t="s">
         <v>28</v>
@@ -8944,6 +9038,280 @@
       </c>
       <c r="V113" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>148</v>
+      </c>
+      <c r="B114" t="s">
+        <v>303</v>
+      </c>
+      <c r="C114" t="s">
+        <v>303</v>
+      </c>
+      <c r="E114" t="s">
+        <v>16</v>
+      </c>
+      <c r="F114" s="2"/>
+      <c r="I114" s="4"/>
+      <c r="L114" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M114" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N114" t="s">
+        <v>278</v>
+      </c>
+      <c r="O114" t="s">
+        <v>307</v>
+      </c>
+      <c r="P114" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q114" s="3"/>
+      <c r="R114" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="U114" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>148</v>
+      </c>
+      <c r="B115" t="s">
+        <v>306</v>
+      </c>
+      <c r="C115" t="s">
+        <v>306</v>
+      </c>
+      <c r="E115" t="s">
+        <v>16</v>
+      </c>
+      <c r="F115" s="2"/>
+      <c r="I115" s="4"/>
+      <c r="L115" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N115"/>
+      <c r="O115"/>
+      <c r="P115" s="5"/>
+      <c r="Q115" s="3"/>
+      <c r="R115" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="U115" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>148</v>
+      </c>
+      <c r="B116" t="s">
+        <v>282</v>
+      </c>
+      <c r="C116" t="s">
+        <v>282</v>
+      </c>
+      <c r="E116" t="s">
+        <v>16</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R116" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="U116" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>148</v>
+      </c>
+      <c r="B117" t="s">
+        <v>298</v>
+      </c>
+      <c r="C117" t="s">
+        <v>298</v>
+      </c>
+      <c r="E117" t="s">
+        <v>16</v>
+      </c>
+      <c r="L117" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R117" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="U117" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>148</v>
+      </c>
+      <c r="B118" t="s">
+        <v>299</v>
+      </c>
+      <c r="C118" t="s">
+        <v>299</v>
+      </c>
+      <c r="E118" t="s">
+        <v>16</v>
+      </c>
+      <c r="L118" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R118" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="U118" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>148</v>
+      </c>
+      <c r="B119" t="s">
+        <v>283</v>
+      </c>
+      <c r="C119" t="s">
+        <v>283</v>
+      </c>
+      <c r="E119" t="s">
+        <v>16</v>
+      </c>
+      <c r="L119" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R119" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="U119" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>148</v>
+      </c>
+      <c r="B120" t="s">
+        <v>284</v>
+      </c>
+      <c r="C120" t="s">
+        <v>284</v>
+      </c>
+      <c r="E120" t="s">
+        <v>16</v>
+      </c>
+      <c r="L120" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R120" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="U120" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>148</v>
+      </c>
+      <c r="B121" t="s">
+        <v>285</v>
+      </c>
+      <c r="C121" t="s">
+        <v>285</v>
+      </c>
+      <c r="E121" t="s">
+        <v>16</v>
+      </c>
+      <c r="L121" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R121" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="U121" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>148</v>
+      </c>
+      <c r="B122" t="s">
+        <v>286</v>
+      </c>
+      <c r="C122" t="s">
+        <v>300</v>
+      </c>
+      <c r="E122" t="s">
+        <v>16</v>
+      </c>
+      <c r="L122" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R122" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="U122" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>148</v>
+      </c>
+      <c r="B123" t="s">
+        <v>288</v>
+      </c>
+      <c r="C123" t="s">
+        <v>301</v>
+      </c>
+      <c r="E123" t="s">
+        <v>16</v>
+      </c>
+      <c r="L123" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R123" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="U123" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>148</v>
+      </c>
+      <c r="B124" t="s">
+        <v>287</v>
+      </c>
+      <c r="C124" t="s">
+        <v>302</v>
+      </c>
+      <c r="E124" t="s">
+        <v>16</v>
+      </c>
+      <c r="L124" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R124" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="U124" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
